--- a/data/WP18/WP18_uebersicht.xlsx
+++ b/data/WP18/WP18_uebersicht.xlsx
@@ -387,7 +387,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>5351</v>
+        <v>5797</v>
       </c>
     </row>
     <row r="5">
@@ -395,7 +395,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>27.1179515118496</v>
+        <v>21.043312448924</v>
       </c>
     </row>
   </sheetData>
@@ -632,13 +632,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE432FC8-3289-47EF-8C1F-E668967ABCDB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB0A8C0E-B177-4CBA-8117-2EF57CEBBDFE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33F15E3D-7142-4767-BD4C-7690984A4475}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{241FD5A8-A9E4-4301-9E6A-985ACBD279C6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04D8CE12-83FE-401A-B5D0-B6FC240F1D36}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D50BEEF-E416-43DE-AC59-C25C31056256}"/>
 </file>